--- a/artfynd/A 18957-2024 artfynd.xlsx
+++ b/artfynd/A 18957-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117949101</v>
+        <v>117950722</v>
       </c>
       <c r="B2" t="n">
-        <v>103349</v>
+        <v>42953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720355</v>
+        <v>720388</v>
       </c>
       <c r="R2" t="n">
-        <v>6370000</v>
+        <v>6370012</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +776,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog, stig. Grusrygg.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117950722</v>
+        <v>117949101</v>
       </c>
       <c r="B3" t="n">
-        <v>42953</v>
+        <v>103349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,54 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101242</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720388</v>
+        <v>720355</v>
       </c>
       <c r="R3" t="n">
-        <v>6370012</v>
+        <v>6370000</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,19 +879,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog, stig. Grusrygg.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 18957-2024 artfynd.xlsx
+++ b/artfynd/A 18957-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117950722</v>
+        <v>117949092</v>
       </c>
       <c r="B2" t="n">
-        <v>42953</v>
+        <v>100097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720388</v>
+        <v>720424</v>
       </c>
       <c r="R2" t="n">
-        <v>6370012</v>
+        <v>6369974</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,29 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrskog. Grusrygg.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117949101</v>
+        <v>117949088</v>
       </c>
       <c r="B3" t="n">
-        <v>103349</v>
+        <v>108703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720355</v>
+        <v>720486</v>
       </c>
       <c r="R3" t="n">
-        <v>6370000</v>
+        <v>6369996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallskog, stig. Grusrygg.</t>
+          <t>Barrskog. Grusrygg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117949061</v>
+        <v>117949098</v>
       </c>
       <c r="B4" t="n">
         <v>108703</v>
@@ -942,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720536</v>
+        <v>720355</v>
       </c>
       <c r="R4" t="n">
-        <v>6369689</v>
+        <v>6370000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +978,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallskog på åsrygg.</t>
+          <t>Tallskog, stig. Grusrygg.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1009,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117949098</v>
+        <v>117949059</v>
       </c>
       <c r="B5" t="n">
         <v>108703</v>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720355</v>
+        <v>720552</v>
       </c>
       <c r="R5" t="n">
-        <v>6370000</v>
+        <v>6369675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1074,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvårdshänsyn, snitsel vid dike i sumpskog.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1098,7 +1090,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallskog, stig. Grusrygg.</t>
+          <t>Sumpskog vid dike.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1116,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117950525</v>
+        <v>117949101</v>
       </c>
       <c r="B6" t="n">
-        <v>44521</v>
+        <v>103349</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,54 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201164</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720388</v>
+        <v>720355</v>
       </c>
       <c r="R6" t="n">
-        <v>6370012</v>
+        <v>6370000</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,26 +1192,30 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog, stig. Grusrygg.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117949081</v>
+        <v>117949061</v>
       </c>
       <c r="B7" t="n">
         <v>108703</v>
@@ -1276,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720506</v>
+        <v>720536</v>
       </c>
       <c r="R7" t="n">
-        <v>6369988</v>
+        <v>6369689</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,11 +1293,6 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Naturvårdssnitsel i gran vid stor tall.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1330,7 +1304,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
+          <t>Tallskog på åsrygg.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1348,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117949082</v>
+        <v>117950492</v>
       </c>
       <c r="B8" t="n">
-        <v>97859</v>
+        <v>42784</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,41 +1334,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>101260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720506</v>
+        <v>720388</v>
       </c>
       <c r="R8" t="n">
-        <v>6369988</v>
+        <v>6370012</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,17 +1409,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Naturvårdssnitsel i gran vid stor tall.</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,33 +1423,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117949059</v>
+        <v>117950722</v>
       </c>
       <c r="B9" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,37 +1458,54 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720552</v>
+        <v>720388</v>
       </c>
       <c r="R9" t="n">
-        <v>6369675</v>
+        <v>6370012</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,17 +1529,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Naturvårdshänsyn, snitsel vid dike i sumpskog.</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,33 +1543,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Sumpskog vid dike.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117950492</v>
+        <v>117950525</v>
       </c>
       <c r="B10" t="n">
-        <v>42784</v>
+        <v>44521</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,16 +1578,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101260</v>
+        <v>201164</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1659,12 +1649,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117949056</v>
+        <v>117949082</v>
       </c>
       <c r="B11" t="n">
-        <v>96791</v>
+        <v>97859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,43 +1698,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720584</v>
+        <v>720506</v>
       </c>
       <c r="R11" t="n">
-        <v>6369744</v>
+        <v>6369988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1762,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Härifrån sandig tallskog ända till skogsstuga NV agmyr mot NO.</t>
+          <t>Naturvårdssnitsel i gran vid stor tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1776,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Tallskog på sandig åsrygg.</t>
+          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1813,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117948986</v>
+        <v>117949081</v>
       </c>
       <c r="B12" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,53 +1810,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720424</v>
+        <v>720506</v>
       </c>
       <c r="R12" t="n">
-        <v>6369974</v>
+        <v>6369988</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1874,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Viss osäkerhet; snabb observation.</t>
+          <t>Naturvårdssnitsel i gran vid stor tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,7 +1888,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrskog.</t>
+          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1944,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117949084</v>
+        <v>117949085</v>
       </c>
       <c r="B13" t="n">
-        <v>97870</v>
+        <v>97814</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,26 +1922,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2065,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117949103</v>
+        <v>117948986</v>
       </c>
       <c r="B14" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,21 +2043,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2105,7 +2067,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2114,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720359</v>
+        <v>720424</v>
       </c>
       <c r="R14" t="n">
-        <v>6370005</v>
+        <v>6369974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,6 +2124,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet; snabb observation.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2163,7 +2140,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallskog, stig. Grusrygg.</t>
+          <t>Barrskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2181,7 +2158,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117949088</v>
+        <v>117949103</v>
       </c>
       <c r="B15" t="n">
         <v>108703</v>
@@ -2214,17 +2191,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720486</v>
+        <v>720359</v>
       </c>
       <c r="R15" t="n">
-        <v>6369996</v>
+        <v>6370005</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,7 +2256,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrskog. Grusrygg.</t>
+          <t>Tallskog, stig. Grusrygg.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2404,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117949092</v>
+        <v>117949056</v>
       </c>
       <c r="B17" t="n">
-        <v>100097</v>
+        <v>96791</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,34 +2406,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720424</v>
+        <v>720584</v>
       </c>
       <c r="R17" t="n">
-        <v>6369974</v>
+        <v>6369744</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,6 +2477,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Härifrån sandig tallskog ända till skogsstuga NV agmyr mot NO.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrskog. Grusrygg.</t>
+          <t>Tallskog på sandig åsrygg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117949085</v>
+        <v>117949084</v>
       </c>
       <c r="B18" t="n">
-        <v>97814</v>
+        <v>97870</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,26 +2527,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">

--- a/artfynd/A 18957-2024 artfynd.xlsx
+++ b/artfynd/A 18957-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117949092</v>
+        <v>117950722</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
+        <v>42953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>101242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720424</v>
+        <v>720388</v>
       </c>
       <c r="R2" t="n">
-        <v>6369974</v>
+        <v>6370012</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +762,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +776,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog. Grusrygg.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117949088</v>
+        <v>117949082</v>
       </c>
       <c r="B3" t="n">
-        <v>108703</v>
+        <v>97861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720486</v>
+        <v>720506</v>
       </c>
       <c r="R3" t="n">
-        <v>6369996</v>
+        <v>6369988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +873,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Naturvårdssnitsel i gran vid stor tall.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Grusrygg.</t>
+          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -889,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117949098</v>
+        <v>117949103</v>
       </c>
       <c r="B4" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,17 +940,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720355</v>
+        <v>720359</v>
       </c>
       <c r="R4" t="n">
-        <v>6370000</v>
+        <v>6370005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117949059</v>
+        <v>117949056</v>
       </c>
       <c r="B5" t="n">
-        <v>108703</v>
+        <v>96793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,20 +1035,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,17 +1056,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720552</v>
+        <v>720584</v>
       </c>
       <c r="R5" t="n">
-        <v>6369675</v>
+        <v>6369744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1112,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Naturvårdshänsyn, snitsel vid dike i sumpskog.</t>
+          <t>Härifrån sandig tallskog ända till skogsstuga NV agmyr mot NO.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,7 +1126,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Sumpskog vid dike.</t>
+          <t>Tallskog på sandig åsrygg.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1108,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117949101</v>
+        <v>117949081</v>
       </c>
       <c r="B6" t="n">
-        <v>103349</v>
+        <v>108705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1160,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720355</v>
+        <v>720506</v>
       </c>
       <c r="R6" t="n">
-        <v>6370000</v>
+        <v>6369988</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1222,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Naturvårdssnitsel i gran vid stor tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1197,7 +1238,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Tallskog, stig. Grusrygg.</t>
+          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1215,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117949061</v>
+        <v>117950438</v>
       </c>
       <c r="B7" t="n">
-        <v>108703</v>
+        <v>42784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,37 +1272,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>101260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720536</v>
+        <v>720388</v>
       </c>
       <c r="R7" t="n">
-        <v>6369689</v>
+        <v>6370012</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,12 +1343,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,33 +1357,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallskog på åsrygg.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117950492</v>
+        <v>117949092</v>
       </c>
       <c r="B8" t="n">
-        <v>42784</v>
+        <v>100099</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,58 +1388,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101260</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720388</v>
+        <v>720424</v>
       </c>
       <c r="R8" t="n">
-        <v>6370012</v>
+        <v>6369974</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,29 +1460,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog. Grusrygg.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117950722</v>
+        <v>117949085</v>
       </c>
       <c r="B9" t="n">
-        <v>42953</v>
+        <v>97816</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,58 +1495,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101242</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720388</v>
+        <v>720506</v>
       </c>
       <c r="R9" t="n">
-        <v>6370012</v>
+        <v>6369988</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,12 +1562,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-11</t>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvårdssnitsel i gran vid stor tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,29 +1581,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117950525</v>
+        <v>117949098</v>
       </c>
       <c r="B10" t="n">
-        <v>44521</v>
+        <v>108705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,54 +1620,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201164</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SO om Hambrars, Gtl</t>
+          <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720388</v>
+        <v>720355</v>
       </c>
       <c r="R10" t="n">
-        <v>6370012</v>
+        <v>6370000</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,12 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,29 +1688,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog, stig. Grusrygg.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebbe Nilsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117949082</v>
+        <v>117950525</v>
       </c>
       <c r="B11" t="n">
-        <v>97859</v>
+        <v>44521</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,41 +1723,58 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>201164</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Botvatte 1:26 (2), Gtl</t>
+          <t>SO om Hambrars, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720506</v>
+        <v>720388</v>
       </c>
       <c r="R11" t="n">
-        <v>6369988</v>
+        <v>6370012</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,17 +1798,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Naturvårdssnitsel i gran vid stor tall.</t>
+          <t>2014-07-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,33 +1812,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sebbe Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117949081</v>
+        <v>117949084</v>
       </c>
       <c r="B12" t="n">
-        <v>108703</v>
+        <v>97872</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,28 +1843,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
@@ -1906,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117949085</v>
+        <v>117949088</v>
       </c>
       <c r="B13" t="n">
-        <v>97814</v>
+        <v>108705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,47 +1964,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720506</v>
+        <v>720486</v>
       </c>
       <c r="R13" t="n">
-        <v>6369988</v>
+        <v>6369996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,11 +2030,6 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Naturvårdssnitsel i gran vid stor tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2009,7 +2041,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
+          <t>Barrskog. Grusrygg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2027,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117948986</v>
+        <v>117949101</v>
       </c>
       <c r="B14" t="n">
-        <v>42953</v>
+        <v>103351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,53 +2075,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101242</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720424</v>
+        <v>720355</v>
       </c>
       <c r="R14" t="n">
-        <v>6369974</v>
+        <v>6370000</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,11 +2137,6 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Viss osäkerhet; snabb observation.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2140,7 +2148,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrskog.</t>
+          <t>Tallskog, stig. Grusrygg.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2158,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117949103</v>
+        <v>117948986</v>
       </c>
       <c r="B15" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2198,7 +2206,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2207,10 +2225,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720359</v>
+        <v>720424</v>
       </c>
       <c r="R15" t="n">
-        <v>6370005</v>
+        <v>6369974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,6 +2263,11 @@
           <t>2024-06-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Viss osäkerhet; snabb observation.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2256,7 +2279,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallskog, stig. Grusrygg.</t>
+          <t>Barrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2277,7 +2300,7 @@
         <v>117949097</v>
       </c>
       <c r="B16" t="n">
-        <v>106765</v>
+        <v>106767</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2390,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117949056</v>
+        <v>117949059</v>
       </c>
       <c r="B17" t="n">
-        <v>96791</v>
+        <v>108705</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,20 +2425,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2423,26 +2446,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720584</v>
+        <v>720552</v>
       </c>
       <c r="R17" t="n">
-        <v>6369744</v>
+        <v>6369675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,7 +2493,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Härifrån sandig tallskog ända till skogsstuga NV agmyr mot NO.</t>
+          <t>Naturvårdshänsyn, snitsel vid dike i sumpskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,7 +2507,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Tallskog på sandig åsrygg.</t>
+          <t>Sumpskog vid dike.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2511,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117949084</v>
+        <v>117949061</v>
       </c>
       <c r="B18" t="n">
-        <v>97870</v>
+        <v>108705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,47 +2537,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Botvatte 1:26 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720506</v>
+        <v>720536</v>
       </c>
       <c r="R18" t="n">
-        <v>6369988</v>
+        <v>6369689</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,11 +2603,6 @@
           <t>2024-06-21</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Naturvårdssnitsel i gran vid stor tall.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrskog, frisk mark, dikat. Träd på socklar.</t>
+          <t>Tallskog på åsrygg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
